--- a/Tipologias/Tipos de Reboque/Frigorifico/Bi Temperatura/Especificações Técnicas e Descrição.xlsx
+++ b/Tipologias/Tipos de Reboque/Frigorifico/Bi Temperatura/Especificações Técnicas e Descrição.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/artiom_fedco_tja_pt/Documents/Ambiente de Trabalho/Tipologias/Tipologias/Tipos de Reboque/Frigorifico/Bi Temperatura/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/artiom_fedco_tja_pt/Documents/Ambiente de Trabalho/Tipologias/Tipologias/Tipos de Reboque/Frigorífico/Bi Temperatura/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4A39029-2363-415D-BB45-30077AC0E66C}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6276951C-F02F-4BBE-A82D-5F5B68DB7EF6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>COMPRIMENTO</t>
   </si>
@@ -76,6 +76,21 @@
   </si>
   <si>
     <t>39000 kg</t>
+  </si>
+  <si>
+    <t>Verificar o funcionamento do motor do frigorífico.
+Verificar e efetuar a limpeza do interior do reboque.
+Verificar o nível de combustível do frigorífico.
+Confirmar a presença e o estado do equipamento: colchões e prumos.
+Quando o reboque estiver vazio e limpo, deixá-lo com as portas abertas, sempre que possível.</t>
+  </si>
+  <si>
+    <t>Verificar a temperatura em cada paragem.
+Verificar o nível de combustível do frigorífico.</t>
+  </si>
+  <si>
+    <t>Manter os colchões sempre arrumados junto ao evaporador, na posição vertical.
+Verificar os alarmes do motor e comunicar qualquer anomalia ao gestor.</t>
   </si>
 </sst>
 </file>
@@ -111,10 +126,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -400,7 +418,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -466,19 +484,28 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Tipologias/Tipos de Reboque/Frigorifico/Bi Temperatura/Especificações Técnicas e Descrição.xlsx
+++ b/Tipologias/Tipos de Reboque/Frigorifico/Bi Temperatura/Especificações Técnicas e Descrição.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/artiom_fedco_tja_pt/Documents/Ambiente de Trabalho/Tipologias/Tipologias/Tipos de Reboque/Frigorífico/Bi Temperatura/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6276951C-F02F-4BBE-A82D-5F5B68DB7EF6}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{127135A9-D5CF-4B04-8D6D-7A4E427BBE2C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,32 +78,38 @@
     <t>39000 kg</t>
   </si>
   <si>
-    <t>Verificar o funcionamento do motor do frigorífico.
-Verificar e efetuar a limpeza do interior do reboque.
-Verificar o nível de combustível do frigorífico.
-Confirmar a presença e o estado do equipamento: colchões e prumos.
-Quando o reboque estiver vazio e limpo, deixá-lo com as portas abertas, sempre que possível.</t>
-  </si>
-  <si>
-    <t>Verificar a temperatura em cada paragem.
-Verificar o nível de combustível do frigorífico.</t>
-  </si>
-  <si>
-    <t>Manter os colchões sempre arrumados junto ao evaporador, na posição vertical.
-Verificar os alarmes do motor e comunicar qualquer anomalia ao gestor.</t>
+    <t>• Verificar o funcionamento do motor do frigorífico.
+• Verificar e efetuar a limpeza do interior do reboque.
+• Verificar o nível de combustível do frigorífico.
+• Confirmar a presença e o estado do equipamento: colchões e prumos.
+• Quando o reboque estiver vazio e limpo, deixá-lo com as portas abertas, sempre que possível.</t>
+  </si>
+  <si>
+    <t>• Verificar a temperatura em cada paragem.
+• Verificar o nível de combustível do frigorífico.</t>
+  </si>
+  <si>
+    <t>• Manter os colchões sempre arrumados junto ao evaporador, na posição vertical.
+• Verificar os alarmes do motor e comunicar qualquer anomalia ao gestor.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -126,12 +132,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -418,7 +427,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="78.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -484,11 +493,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -500,7 +509,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -510,5 +519,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Tipologias/Tipos de Reboque/Frigorifico/Bi Temperatura/Especificações Técnicas e Descrição.xlsx
+++ b/Tipologias/Tipos de Reboque/Frigorifico/Bi Temperatura/Especificações Técnicas e Descrição.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/artiom_fedco_tja_pt/Documents/Ambiente de Trabalho/Tipologias/Tipologias/Tipos de Reboque/Frigorífico/Bi Temperatura/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{127135A9-D5CF-4B04-8D6D-7A4E427BBE2C}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C8DFB8C-B4C8-440E-ABF4-8907FCEB5CC3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>COMPRIMENTO</t>
   </si>
@@ -91,6 +91,9 @@
   <si>
     <t>• Manter os colchões sempre arrumados junto ao evaporador, na posição vertical.
 • Verificar os alarmes do motor e comunicar qualquer anomalia ao gestor.</t>
+  </si>
+  <si>
+    <t>Um reboque frigorífico bi-temperatura permite transportar, em simultâneo, produtos que necessitam de duas temperaturas diferentes, mantendo cada compartimento nas condições adequadas.</t>
   </si>
 </sst>
 </file>
@@ -492,6 +495,9 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="9" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
